--- a/data/words_v3_exampleko_502_1001.xlsx
+++ b/data/words_v3_exampleko_502_1001.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H3000"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
   <cols>
     <col width="18" customWidth="1" style="29" min="1" max="1"/>
     <col width="24" customWidth="1" style="29" min="2" max="2"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>일부 textile fabrics은 내용이나 실질이 부족합니다.  [초안]</t>
+          <t>일부 직물은 내용이나 실질이 부족합니다.  [초안]</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -37593,7 +37593,7 @@
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>일부 주민들은 그 제안이 사실보다 감정에 치우쳐 있다며 이의를 제기했습니다.  [초안]</t>
+          <t>일부 주민들은 그 제안이 사실보다 감정에 치우쳐 있다며 이의를 제기했습니다.</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>어떤 사람들은 자신이 사는 도시 안에서만 유명합니다.  [초안]</t>
+          <t>어떤 사람들은 자신이 사는 도시 안에서만 유명합니다.</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -37669,7 +37669,7 @@
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>어떤 사람들은 sports.에 지나치게 몰두합니다.  [초안]</t>
+          <t>어떤 사람들은 스포츠에 지나치게 몰두합니다.</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -37823,7 +37823,7 @@
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>사회적 긴장이 최근의 정치적인 위기로 인해 고조되었습니다.</t>
+          <t>최근의 정치적인 위기로 인해 사회적 긴장이 고조되었습니다.</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -38090,7 +38090,7 @@
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>존스미스경과 스미스부인</t>
+          <t>존 스미스경과 스미스 부인</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
@@ -38128,7 +38128,7 @@
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>이 예문에서 'advocate'는 '변호사'의 의미로 쓰였습니다. 자연스러운 한국어 문장으로 다듬어 주세요.  [초안]</t>
+          <t>그녀가 그녀의 변호사와 함께 일을 하게 되면서, 그녀는 더욱더 확신을 가지게 되었습니다.</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
@@ -38165,6 +38165,27 @@
           <t>Since he put on weight, his jeans have been a tight fit.</t>
         </is>
       </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>그가 몸무게가 늘었기 때문에, 그의 청바지가 더욱 타이트한 핏이 되었습니다.</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>fit = 맞는. 예문 속 문맥과 함께 뜻을 기억하세요.</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr"/>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -38182,6 +38203,27 @@
           <t>Show all the spoils by valiant kings achieved.</t>
         </is>
       </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>이 예문에서 'achieve'는 '성취하다'의 의미로 쓰였습니다. 자연스러운 한국어 문장으로 다듬어 주세요.  [초안]</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>achieve = 성취하다. 예문 속 문맥과 함께 뜻을 기억하세요.</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr"/>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
@@ -73929,7 +73971,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D413"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
   <cols>
     <col width="16" customWidth="1" style="29" min="1" max="2"/>
     <col width="38.69921875" customWidth="1" style="29" min="3" max="4"/>
@@ -83033,7 +83075,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="29" min="1" max="1"/>
     <col width="70" customWidth="1" style="29" min="2" max="2"/>
@@ -83142,8 +83184,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="29" min="1" max="1"/>
     <col width="24" customWidth="1" style="29" min="2" max="2"/>
@@ -83286,6 +83328,23 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-07 13:14:53</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dictionary_editor_qt_v2.5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Saved from Editor v2.5 Production Mode</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/words_v3_exampleko_502_1001.xlsx
+++ b/data/words_v3_exampleko_502_1001.xlsx
@@ -37573,7 +37573,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1002" t="inlineStr"/>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -37611,7 +37610,6 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="H1003" t="inlineStr"/>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
@@ -37649,7 +37647,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1004" t="inlineStr"/>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -37688,7 +37685,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1005" t="inlineStr"/>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -37726,7 +37722,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1006" t="inlineStr"/>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
@@ -37764,7 +37759,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1007" t="inlineStr"/>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -37803,7 +37797,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1008" t="inlineStr"/>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
@@ -37841,7 +37834,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1009" t="inlineStr"/>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
@@ -37879,7 +37871,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1010" t="inlineStr"/>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
@@ -37917,7 +37908,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1011" t="inlineStr"/>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -37955,7 +37945,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1012" t="inlineStr"/>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
@@ -37993,7 +37982,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1013" t="inlineStr"/>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -38031,7 +38019,6 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="H1014" t="inlineStr"/>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -38070,7 +38057,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1015" t="inlineStr"/>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
@@ -38108,7 +38094,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1016" t="inlineStr"/>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
@@ -38147,7 +38132,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1017" t="inlineStr"/>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
@@ -38185,7 +38169,6 @@
           <t>Daily</t>
         </is>
       </c>
-      <c r="H1018" t="inlineStr"/>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -38205,7 +38188,7 @@
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>이 예문에서 'achieve'는 '성취하다'의 의미로 쓰였습니다. 자연스러운 한국어 문장으로 다듬어 주세요.  [초안]</t>
+          <t>용맹한 왕들이 이룬 모든 전리품을 보여주세요.</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -38241,6 +38224,27 @@
           <t>Shoulder the blame.</t>
         </is>
       </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>비난을 어깨에 짊어지다(=총대를 메다, 죄를 뒤집어 쓰다)</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>shoulder = 어깨. 예문 속 문맥과 함께 뜻을 기억하세요.</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr"/>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
@@ -38258,6 +38262,27 @@
           <t>Should we classify "make up" as an idiom or as a phrasal verb?</t>
         </is>
       </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>"make up"을 관용구로 분류해야 할까요, 아니면 구술 동사로 분류해야 할까요?</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>classify = 분류하다. 예문 속 문맥과 함께 뜻을 기억하세요.</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr"/>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
@@ -38275,6 +38300,27 @@
           <t>She's the first athlete in her sport to obtain a corporate sponsor.</t>
         </is>
       </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>athlete가 '운동가'의 뜻으로 쓰인 예문입니다. 문맥에 맞게 한국어로 다듬어 주세요.  [초안]</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>athlete = 운동가. 예문 속 문맥과 함께 뜻을 기억하세요.</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr"/>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
@@ -83184,7 +83230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="29" min="1" max="1"/>
@@ -83345,6 +83391,40 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-07 15:16:50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dictionary_editor_qt_v2.5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Saved from Editor v2.5 Production Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-07 15:36:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dictionary_editor_qt_v2.5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Saved from Editor v2.5 Production Mode</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/words_v3_exampleko_502_1001.xlsx
+++ b/data/words_v3_exampleko_502_1001.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H3000"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="29" min="1" max="1"/>
     <col width="24" customWidth="1" style="29" min="2" max="2"/>
@@ -37573,6 +37573,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1002" t="inlineStr"/>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -37610,6 +37611,7 @@
           <t>Business</t>
         </is>
       </c>
+      <c r="H1003" t="inlineStr"/>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
@@ -37647,6 +37649,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1004" t="inlineStr"/>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -37685,6 +37688,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1005" t="inlineStr"/>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -37722,6 +37726,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1006" t="inlineStr"/>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
@@ -37759,6 +37764,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1007" t="inlineStr"/>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -37797,6 +37803,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1008" t="inlineStr"/>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
@@ -37834,6 +37841,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1009" t="inlineStr"/>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
@@ -37871,6 +37879,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1010" t="inlineStr"/>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
@@ -37908,6 +37917,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1011" t="inlineStr"/>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -37945,6 +37955,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1012" t="inlineStr"/>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
@@ -37982,6 +37993,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1013" t="inlineStr"/>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -38019,6 +38031,7 @@
           <t>Travel</t>
         </is>
       </c>
+      <c r="H1014" t="inlineStr"/>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -38057,6 +38070,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1015" t="inlineStr"/>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
@@ -38094,6 +38108,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1016" t="inlineStr"/>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
@@ -38132,6 +38147,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1017" t="inlineStr"/>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
@@ -38169,6 +38185,7 @@
           <t>Daily</t>
         </is>
       </c>
+      <c r="H1018" t="inlineStr"/>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -38302,7 +38319,7 @@
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>athlete가 '운동가'의 뜻으로 쓰인 예문입니다. 문맥에 맞게 한국어로 다듬어 주세요.  [초안]</t>
+          <t>그녀는 그녀의 스포츠 분야에서 기업 스폰서십을 받은 첫번째 선수입니다.</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
@@ -38338,6 +38355,27 @@
           <t>She's taller than I am;  she found his advice more witty than helpful;  we have less work today than we had yesterday;  We had no choice than to return home.</t>
         </is>
       </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>그녀는 나보다 키가 크고, 그의 조언이 도움이 되기보다는 재치 있다고 생각했습니다. 우리는 어제보다 오늘 일이 덜하여서, 집으로 돌아가는 것 외에는 선택의 여지가 없었습니다.</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>then = 그때. 예문 속 문맥과 함께 뜻을 기억하세요.</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr"/>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
@@ -38355,6 +38393,27 @@
           <t>She's studying medicine at university because she wants to be a doctor in the future.</t>
         </is>
       </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>medicine가 '약'의 뜻으로 쓰인 예문입니다. 문맥에 맞게 한국어로 다듬어 주세요.  [초안]</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>medicine = 약. 예문 속 문맥과 함께 뜻을 기억하세요.</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>Academic, Medical</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr"/>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
@@ -38372,6 +38431,11 @@
           <t>She's leaving because she faced numerous problems to do with racism.</t>
         </is>
       </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
@@ -38389,6 +38453,11 @@
           <t>She's certainly taken a shine to you.</t>
         </is>
       </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -38406,6 +38475,11 @@
           <t>She's at the height of her career.</t>
         </is>
       </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
@@ -38423,6 +38497,11 @@
           <t>She’ll be coming ’round the mountain when she comes [...].</t>
         </is>
       </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
@@ -38440,6 +38519,11 @@
           <t>She works in retail.</t>
         </is>
       </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -38457,6 +38541,11 @@
           <t>She works for the ministry of finance.</t>
         </is>
       </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
@@ -38474,6 +38563,11 @@
           <t>She wore a tattered jean jacket.</t>
         </is>
       </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
@@ -38491,6 +38585,11 @@
           <t>She will skip from one end of the sidewalk to the other.</t>
         </is>
       </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
@@ -38508,6 +38607,11 @@
           <t>She went into civil service because she wanted to help the people.</t>
         </is>
       </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
@@ -38525,6 +38629,11 @@
           <t>She was worn out from so much grief.</t>
         </is>
       </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
@@ -38542,6 +38651,11 @@
           <t>She was sitting in a jazz club, sipping wine and listening to a bass player's solo.</t>
         </is>
       </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
@@ -38559,6 +38673,11 @@
           <t>She was as naked as the day she was born.</t>
         </is>
       </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -38576,6 +38695,11 @@
           <t>She was a total brain.</t>
         </is>
       </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
@@ -38593,6 +38717,11 @@
           <t>She transferred from the Faculty of Science to the Faculty of Medicine.</t>
         </is>
       </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
@@ -38610,6 +38739,11 @@
           <t>She trained seven hours a day to prepare for the Olympics.</t>
         </is>
       </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
@@ -38627,6 +38761,11 @@
           <t>She took a deep draft from the bottle of water.</t>
         </is>
       </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -38644,6 +38783,11 @@
           <t>She thanked him for the lift.</t>
         </is>
       </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
@@ -38661,6 +38805,11 @@
           <t>She tempted me to eat the apple.</t>
         </is>
       </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -38678,6 +38827,11 @@
           <t>She suffered a terrible collapse after slipping on the wet floor.</t>
         </is>
       </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -38695,6 +38849,11 @@
           <t>She struggled to play the difficult passages.</t>
         </is>
       </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
@@ -38712,6 +38871,11 @@
           <t>She stood with her right arm extended and her palm forward to indicate “Stop!”.</t>
         </is>
       </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -38729,6 +38893,11 @@
           <t>She spent some serious coin on that car!</t>
         </is>
       </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
@@ -38746,6 +38915,11 @@
           <t>She rose before dawn to meet the train.</t>
         </is>
       </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
@@ -38763,6 +38937,11 @@
           <t>She replied in the negative, with a shake of her head.</t>
         </is>
       </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -38780,6 +38959,11 @@
           <t>She received many presents for her birthday.</t>
         </is>
       </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
@@ -38797,6 +38981,11 @@
           <t>She read my fortune. Apparently I will have a good love life this week, but I will have a bad week for money.</t>
         </is>
       </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -38814,6 +39003,11 @@
           <t>She photographs well. The camera loves her.</t>
         </is>
       </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
@@ -38831,6 +39025,11 @@
           <t>She paused for only an instant, which was just enough time for John to change the subject.</t>
         </is>
       </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
@@ -38848,6 +39047,11 @@
           <t>She newspapered one end of the room before painting the bookcase.</t>
         </is>
       </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -38865,6 +39069,11 @@
           <t>She moved toward the door.</t>
         </is>
       </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -38882,6 +39091,11 @@
           <t>She liked to walk in her flats more than in her high heels.</t>
         </is>
       </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
@@ -38899,6 +39113,11 @@
           <t>She is quite mature for her age.</t>
         </is>
       </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
@@ -38916,6 +39135,11 @@
           <t>She has two bachelor's degrees and is studying towards a master's degree.</t>
         </is>
       </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
@@ -38933,6 +39157,11 @@
           <t>She has a great sense of humour, and I always laugh a lot whenever we get together.</t>
         </is>
       </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
@@ -38950,6 +39179,11 @@
           <t>She has a cold in the nose.</t>
         </is>
       </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -38967,6 +39201,11 @@
           <t>She had second-degree burns from falling in the bonfire.</t>
         </is>
       </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
@@ -38984,6 +39223,11 @@
           <t>She had ambitions beyond her station.</t>
         </is>
       </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
@@ -39001,6 +39245,11 @@
           <t>She had a gift for playing the flute.</t>
         </is>
       </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -39018,6 +39267,11 @@
           <t>She gave the flowers a quick sniff to check they were real.</t>
         </is>
       </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
@@ -39035,6 +39289,11 @@
           <t>She gave the cat a stroke.</t>
         </is>
       </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -39052,6 +39311,11 @@
           <t>She gave her hair a quick brush.</t>
         </is>
       </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
@@ -39069,6 +39333,11 @@
           <t>She gave her all, and collapsed at the finish line.</t>
         </is>
       </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -39086,6 +39355,11 @@
           <t>She frowned when I told her the news.</t>
         </is>
       </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
@@ -39103,6 +39377,11 @@
           <t>She even rejected my improved offer.</t>
         </is>
       </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
@@ -39120,6 +39399,11 @@
           <t>She drove her car to the mall.</t>
         </is>
       </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
@@ -39137,6 +39421,11 @@
           <t>She couldn't hurt a fly, young slip of a girl that she is.</t>
         </is>
       </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
@@ -39154,6 +39443,11 @@
           <t>She closely resembles her sister.</t>
         </is>
       </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
@@ -39171,6 +39465,11 @@
           <t>She can speak English, French, and German.   I can play football.   Can you remember your fifth birthday?</t>
         </is>
       </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
@@ -39188,6 +39487,11 @@
           <t>She can speak English, French, and German.   I can play football.   Can you remember your fifth birthday?</t>
         </is>
       </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
@@ -39205,6 +39509,11 @@
           <t>She can bear witness, since she was there at the time.</t>
         </is>
       </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
@@ -39222,6 +39531,11 @@
           <t>She brings a wealth of knowledge to the project.</t>
         </is>
       </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
@@ -39239,6 +39553,11 @@
           <t>She associates with her coworkers on weekends.</t>
         </is>
       </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -39256,6 +39575,11 @@
           <t>She accused him of lying.</t>
         </is>
       </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
@@ -39273,6 +39597,11 @@
           <t>Several different scientists all reached this conclusion at about the same time.</t>
         </is>
       </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
@@ -39290,6 +39619,11 @@
           <t>Separate the articles from the headings.</t>
         </is>
       </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
@@ -39307,6 +39641,11 @@
           <t>Secretaries attend to correspondence.</t>
         </is>
       </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
@@ -39324,6 +39663,11 @@
           <t>Sealing wax is available as a cylindrical or rectangular stick.</t>
         </is>
       </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
@@ -39341,6 +39685,11 @@
           <t>Schoolchildren take a battery of standard tests to measure their progress.</t>
         </is>
       </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
@@ -39358,6 +39707,11 @@
           <t>Sarah spooned some apple sauce onto her plate.</t>
         </is>
       </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
@@ -39375,6 +39729,11 @@
           <t>São Paulo is the largest city in South America.</t>
         </is>
       </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
@@ -39392,6 +39751,11 @@
           <t>Samuel Johnson compiled one of the most influential dictionaries of the English language.</t>
         </is>
       </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -39409,6 +39773,11 @@
           <t>Salmon is a fish.</t>
         </is>
       </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
@@ -39426,6 +39795,11 @@
           <t>Saddam Hussein was rumored to have many doubles.</t>
         </is>
       </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
@@ -39443,6 +39817,11 @@
           <t>Sad reacts only.</t>
         </is>
       </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
@@ -39460,6 +39839,11 @@
           <t>Rugby players are of sturdy build.</t>
         </is>
       </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
@@ -39477,6 +39861,11 @@
           <t>Royal mast;  royal sail.</t>
         </is>
       </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -39494,6 +39883,11 @@
           <t>Rough in the shape first, then polish the details.</t>
         </is>
       </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -39511,6 +39905,11 @@
           <t>Roman and medieval football matches were more violent than any modern type of football.</t>
         </is>
       </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -39528,6 +39927,11 @@
           <t>Roger and his fellow workers are to go on strike.</t>
         </is>
       </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -39545,6 +39949,11 @@
           <t>Richard obtained a divorce from his wife some years ago, but hasn't returned to the dating scene.</t>
         </is>
       </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
@@ -39562,6 +39971,11 @@
           <t>Rice is a basic for many Asian villagers.</t>
         </is>
       </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
@@ -39579,6 +39993,11 @@
           <t>Restoration literature is well known for its carefully constructed verse.</t>
         </is>
       </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -39596,6 +40015,11 @@
           <t>Remove that line of code and the script should stop erroring there.</t>
         </is>
       </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
@@ -39613,6 +40037,11 @@
           <t>Remind me to congratulate Dave and Lisa on their wedding.</t>
         </is>
       </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -39630,6 +40059,11 @@
           <t>reluctant agreement</t>
         </is>
       </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -39647,6 +40081,11 @@
           <t>Rebecca had always thought shorts were far superior to pants, as they didn't constantly make her legs itch.</t>
         </is>
       </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
+        </is>
+      </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
@@ -39662,6 +40101,11 @@
       <c r="C1101" t="inlineStr">
         <is>
           <t>Reading such an enlightening book on the subject was of much profit to his studies.</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>missing_example_ko, missing_memo, missing_level, missing_tags</t>
         </is>
       </c>
     </row>
@@ -74017,7 +74461,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D413"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" style="29" min="1" max="2"/>
     <col width="38.69921875" customWidth="1" style="29" min="3" max="4"/>
@@ -83121,7 +83565,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="29" min="1" max="1"/>
     <col width="70" customWidth="1" style="29" min="2" max="2"/>
@@ -83230,8 +83674,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="29" min="1" max="1"/>
     <col width="24" customWidth="1" style="29" min="2" max="2"/>
@@ -83425,6 +83869,40 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-07 17:14:34</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dictionary_editor_qt_v2.6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Saved from Editor v2.6 All-in-One</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:02:55</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dictionary_editor_qt_v2.6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Saved from Editor v2.6 All-in-One</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
